--- a/multi_language_reference_annotated.xlsx
+++ b/multi_language_reference_annotated.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17775"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="198">
   <si>
     <t>Feature</t>
   </si>
@@ -225,6 +225,24 @@
   </si>
   <si>
     <t>JavaScript 的 delete 关键字用于对象属性，但不适用于 Map</t>
+  </si>
+  <si>
+    <t>列表随机取值</t>
+  </si>
+  <si>
+    <t>random.choice(self.list)</t>
+  </si>
+  <si>
+    <t>rand.nextInt(list.size()</t>
+  </si>
+  <si>
+    <t>rand.Next(list.Count)</t>
+  </si>
+  <si>
+    <t>rand() % list.size()</t>
+  </si>
+  <si>
+    <t>Math.floor(Math.random() * this.list.length)</t>
   </si>
   <si>
     <t>类定义</t>
@@ -615,16 +633,8 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -634,9 +644,21 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="WPS灵秀黑"/>
       <charset val="134"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="WPS灵秀黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF6A9955"/>
+      <name val="WPS灵秀黑"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -1101,158 +1123,170 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1600,738 +1634,758 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G32"/>
-  <sheetFormatPr defaultColWidth="44.125" defaultRowHeight="13.5" outlineLevelCol="6"/>
+  <dimension ref="A1:G33"/>
+  <sheetFormatPr defaultColWidth="44.125" defaultRowHeight="15" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="23.875" style="1" customWidth="1"/>
-    <col min="2" max="16384" width="44.125" style="1" customWidth="1"/>
+    <col min="2" max="16384" width="44.125" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="5" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="5" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" s="6" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="5" ht="27" spans="1:7">
-      <c r="A5" s="1" t="s">
+    <row r="5" ht="30" spans="1:7">
+      <c r="A5" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" s="6" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="7" ht="27" spans="1:7">
-      <c r="A7" s="1" t="s">
+    <row r="7" spans="1:7">
+      <c r="A7" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="G7" s="6" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="8" ht="27" spans="1:7">
-      <c r="A8" s="1" t="s">
+    <row r="8" spans="1:7">
+      <c r="A8" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F8" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="G8" s="6" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="F9" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="G9" s="6" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="F10" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="G10" s="6" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="11" ht="27" spans="1:7">
-      <c r="A11" s="1" t="s">
+    <row r="11" ht="30" spans="1:7">
+      <c r="A11" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E11" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="F11" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="G11" s="6" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="1" t="s">
+    <row r="12" spans="1:6">
+      <c r="A12" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="G12" s="1" t="s">
+      <c r="D12" s="5" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="13" ht="27" spans="1:7">
-      <c r="A13" s="1" t="s">
+      <c r="E12" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="F12" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="C13" s="1" t="s">
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="D13" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="F13" s="1" t="s">
+      <c r="B13" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="C13" s="5" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="1" t="s">
+      <c r="D13" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G13" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="B14" s="1" t="s">
+    </row>
+    <row r="14" ht="30" spans="1:7">
+      <c r="A14" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="B14" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="C14" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="D14" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F14" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="F14" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="G14" s="1" t="s">
+      <c r="G14" s="6" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D15" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="E15" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="F15" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="G15" s="1" t="s">
+      <c r="G15" s="6" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="16" ht="27" spans="1:7">
-      <c r="A16" s="1" t="s">
+    <row r="16" spans="1:7">
+      <c r="A16" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D16" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F16" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="E16" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="G16" s="1" t="s">
+      <c r="G16" s="6" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="17" ht="27" spans="1:7">
-      <c r="A17" s="1" t="s">
+    <row r="17" ht="30" spans="1:7">
+      <c r="A17" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D17" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="E17" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="F17" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="G17" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="G17" s="1" t="s">
+    </row>
+    <row r="18" ht="30" spans="1:7">
+      <c r="A18" s="4" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="18" ht="27" spans="1:7">
-      <c r="A18" s="1" t="s">
+      <c r="B18" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="C18" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="D18" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="E18" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="F18" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="G18" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="G18" s="1" t="s">
+    </row>
+    <row r="19" ht="30" spans="1:7">
+      <c r="A19" s="4" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="19" ht="27" spans="1:7">
-      <c r="A19" s="1" t="s">
+      <c r="B19" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="C19" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="D19" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="E19" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="F19" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="G19" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="G19" s="1" t="s">
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="4" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="20" ht="27" spans="1:7">
-      <c r="A20" s="1" t="s">
+      <c r="B20" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="C20" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="D20" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="E20" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="F20" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="G20" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="G20" s="1" t="s">
+    </row>
+    <row r="21" ht="30" spans="1:7">
+      <c r="A21" s="4" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="21" ht="27" spans="1:7">
-      <c r="A21" s="1" t="s">
+      <c r="B21" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="C21" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="D21" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="E21" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="F21" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="F21" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="G21" s="1" t="s">
+      <c r="G21" s="6" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
-      <c r="A22" s="1" t="s">
+    <row r="22" ht="30" spans="1:7">
+      <c r="A22" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="F22" s="1" t="s">
+      <c r="B22" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="G22" s="1" t="s">
+      <c r="C22" s="5" t="s">
         <v>129</v>
       </c>
+      <c r="D22" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="1" t="s">
+      <c r="A23" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="D23" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="E23" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="C23" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="F23" s="1" t="s">
+      <c r="F23" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="G23" s="1" t="s">
+      <c r="G23" s="6" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="1" t="s">
+      <c r="A24" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C24" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="D24" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="E24" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="E24" s="1" t="s">
+      <c r="F24" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="F24" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="G24" s="1" t="s">
+      <c r="G24" s="6" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="1" t="s">
+      <c r="A25" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B25" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C25" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="D25" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="E25" s="1" t="s">
+      <c r="E25" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="F25" s="1" t="s">
+      <c r="F25" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="G25" s="1" t="s">
+      <c r="G25" s="6" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="1" t="s">
+      <c r="A26" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B26" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C26" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="D26" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="E26" s="1" t="s">
+      <c r="E26" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="F26" s="1" t="s">
+      <c r="F26" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="G26" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="G26" s="1" t="s">
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="4" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="27" ht="27" spans="1:7">
-      <c r="A27" s="1" t="s">
+      <c r="B27" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="C27" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="D27" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="E27" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="E27" s="1" t="s">
+      <c r="F27" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="F27" s="1" t="s">
+      <c r="G27" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="G27" s="1" t="s">
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" s="4" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="28" ht="27" spans="1:7">
-      <c r="A28" s="1" t="s">
+      <c r="B28" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="C28" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="D28" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="E28" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="E28" s="1" t="s">
+      <c r="F28" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="F28" s="1" t="s">
+      <c r="G28" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G28" s="1" t="s">
+    </row>
+    <row r="29" ht="30" spans="1:7">
+      <c r="A29" s="4" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="29" ht="27" spans="1:7">
-      <c r="A29" s="1" t="s">
+      <c r="B29" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="C29" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="D29" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="D29" s="1" t="s">
+      <c r="E29" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="E29" s="1" t="s">
+      <c r="F29" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="F29" s="1" t="s">
+      <c r="G29" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="G29" s="1" t="s">
+    </row>
+    <row r="30" ht="28.5" spans="1:7">
+      <c r="A30" s="4" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30" s="1" t="s">
+      <c r="B30" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="C30" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="D30" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="E30" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="E30" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="G30" s="1" t="s">
+      <c r="F30" s="5" t="s">
         <v>180</v>
       </c>
+      <c r="G30" s="6" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="B31" s="1" t="s">
+      <c r="A31" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="B31" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="C31" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="E31" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="F31" s="1" t="s">
+      <c r="D31" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="E31" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="G31" s="1" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="32" ht="27" spans="1:7">
-      <c r="A32" s="1" t="s">
+      <c r="F31" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="G31" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="B32" s="1" t="s">
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="B32" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="C32" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="E32" s="1" t="s">
+      <c r="D32" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="F32" s="1" t="s">
+      <c r="E32" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="G32" s="1" t="s">
+      <c r="F32" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="G32" s="6" t="s">
         <v>191</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="G33" s="6" t="s">
+        <v>197</v>
       </c>
     </row>
   </sheetData>

--- a/multi_language_reference_annotated.xlsx
+++ b/multi_language_reference_annotated.xlsx
@@ -161,7 +161,8 @@
     <t>arr.Remove(x)</t>
   </si>
   <si>
-    <t>arr.erase(remove(arr.begin(), arr.end(), x), arr.end())</t>
+    <t>arr.erase(remove(arr.begin(), arr.end(), x), arr.end())
+pop_back() vector、deque 删除最后一个元素 O(1)（最快）</t>
   </si>
   <si>
     <t>arr.splice(arr.indexOf(x), 1)</t>
@@ -1268,7 +1269,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1279,13 +1280,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1665,726 +1660,726 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="4" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="2" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="5" ht="30" spans="1:7">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="2" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="4" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="G7" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="4" t="s">
+    <row r="8" ht="42.75" spans="1:7">
+      <c r="A8" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="G8" s="2" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="G9" s="6" t="s">
+      <c r="G9" s="2" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="F10" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G10" s="6" t="s">
+      <c r="G10" s="2" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="11" ht="30" spans="1:7">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="F11" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="G11" s="6" t="s">
+      <c r="G11" s="2" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E12" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="F12" s="4" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="E13" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="F13" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="G13" s="6" t="s">
+      <c r="G13" s="2" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="14" ht="30" spans="1:7">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="F14" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="G14" s="6" t="s">
+      <c r="G14" s="2" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="E15" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="F15" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="G15" s="6" t="s">
+      <c r="G15" s="2" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D16" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="E16" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="F16" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="G16" s="6" t="s">
+      <c r="G16" s="2" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="17" ht="30" spans="1:7">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="D17" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="E17" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="F17" s="5" t="s">
+      <c r="F17" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="G17" s="6" t="s">
+      <c r="G17" s="2" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="18" ht="30" spans="1:7">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D18" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="E18" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="F18" s="5" t="s">
+      <c r="F18" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="G18" s="6" t="s">
+      <c r="G18" s="2" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="19" ht="30" spans="1:7">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="D19" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="E19" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="F19" s="5" t="s">
+      <c r="F19" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="G19" s="6" t="s">
+      <c r="G19" s="2" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="D20" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="E20" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="F20" s="5" t="s">
+      <c r="F20" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="G20" s="6" t="s">
+      <c r="G20" s="2" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="21" ht="30" spans="1:7">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="D21" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="E21" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="F21" s="5" t="s">
+      <c r="F21" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="G21" s="6" t="s">
+      <c r="G21" s="2" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="22" ht="30" spans="1:7">
-      <c r="A22" s="4" t="s">
+      <c r="A22" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="D22" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="E22" s="5" t="s">
+      <c r="E22" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="F22" s="5" t="s">
+      <c r="F22" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="G22" s="6" t="s">
+      <c r="G22" s="2" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="4" t="s">
+      <c r="A23" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="D23" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="E23" s="5" t="s">
+      <c r="E23" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="F23" s="5" t="s">
+      <c r="F23" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="G23" s="6" t="s">
+      <c r="G23" s="2" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="D24" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="E24" s="5" t="s">
+      <c r="E24" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="F24" s="5" t="s">
+      <c r="F24" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="G24" s="6" t="s">
+      <c r="G24" s="2" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="C25" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="D25" s="5" t="s">
+      <c r="D25" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="E25" s="5" t="s">
+      <c r="E25" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="F25" s="5" t="s">
+      <c r="F25" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="G25" s="6" t="s">
+      <c r="G25" s="2" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="C26" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="D26" s="5" t="s">
+      <c r="D26" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="E26" s="5" t="s">
+      <c r="E26" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="F26" s="5" t="s">
+      <c r="F26" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="G26" s="6" t="s">
+      <c r="G26" s="2" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="C27" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="D27" s="5" t="s">
+      <c r="D27" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="E27" s="5" t="s">
+      <c r="E27" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="F27" s="5" t="s">
+      <c r="F27" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="G27" s="6" t="s">
+      <c r="G27" s="2" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="4" t="s">
+      <c r="A28" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="C28" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="D28" s="5" t="s">
+      <c r="D28" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="E28" s="5" t="s">
+      <c r="E28" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="F28" s="5" t="s">
+      <c r="F28" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="G28" s="6" t="s">
+      <c r="G28" s="2" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="29" ht="30" spans="1:7">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="C29" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="D29" s="5" t="s">
+      <c r="D29" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="E29" s="5" t="s">
+      <c r="E29" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="F29" s="5" t="s">
+      <c r="F29" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="G29" s="6" t="s">
+      <c r="G29" s="2" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="30" ht="28.5" spans="1:7">
-      <c r="A30" s="4" t="s">
+      <c r="A30" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="C30" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="D30" s="5" t="s">
+      <c r="D30" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="E30" s="5" t="s">
+      <c r="E30" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="F30" s="5" t="s">
+      <c r="F30" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="G30" s="6" t="s">
+      <c r="G30" s="2" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="4" t="s">
+      <c r="A31" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B31" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="C31" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="D31" s="5" t="s">
+      <c r="D31" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="E31" s="5" t="s">
+      <c r="E31" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="F31" s="5" t="s">
+      <c r="F31" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="G31" s="6" t="s">
+      <c r="G31" s="2" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="4" t="s">
+      <c r="A32" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="B32" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="C32" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="D32" s="5" t="s">
+      <c r="D32" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="E32" s="5" t="s">
+      <c r="E32" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="F32" s="5" t="s">
+      <c r="F32" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="G32" s="6" t="s">
+      <c r="G32" s="2" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="4" t="s">
+      <c r="A33" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="B33" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="C33" s="5" t="s">
+      <c r="C33" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="D33" s="5" t="s">
+      <c r="D33" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="E33" s="5" t="s">
+      <c r="E33" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="F33" s="5" t="s">
+      <c r="F33" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="G33" s="6" t="s">
+      <c r="G33" s="2" t="s">
         <v>197</v>
       </c>
     </row>
